--- a/artfynd/A 54486-2024 artfynd.xlsx
+++ b/artfynd/A 54486-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90725103</v>
+        <v>90725099</v>
       </c>
       <c r="B2" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>219788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578409.6569474156</v>
+        <v>578410</v>
       </c>
       <c r="R2" t="n">
-        <v>7045777.46617284</v>
+        <v>7045777</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -752,19 +747,9 @@
           <t>2020-06-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90725099</v>
+        <v>90725103</v>
       </c>
       <c r="B3" t="n">
-        <v>96242</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219788</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578409.6569474156</v>
+        <v>578410</v>
       </c>
       <c r="R3" t="n">
-        <v>7045777.46617284</v>
+        <v>7045777</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -869,19 +849,9 @@
           <t>2020-06-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +876,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96282567</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NA, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>578712</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7045733</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Beren van Duijn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54486-2024 artfynd.xlsx
+++ b/artfynd/A 54486-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90725099</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90725103</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,8 +992,18 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96282567</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>